--- a/casos_detective.xlsx
+++ b/casos_detective.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Python\Proyecto_forense\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DB3B67-08E4-422C-8360-E04530EF6293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AC6C75-1257-4533-93CB-D45B00496043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Casos" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="114">
   <si>
     <t>id</t>
   </si>
@@ -343,6 +343,54 @@
   </si>
   <si>
     <t>Para que un cuerpo de este volumen haya alcanzado una temperatura tan baja a pesar de su resistencia térmica, deben haber pasado alrededor de 20 a 24 horas.</t>
+  </si>
+  <si>
+    <t>Caso #09</t>
+  </si>
+  <si>
+    <t>Sujeto masculino de 32 años es ingresado de urgencia a un hospital tras haber participado en una riña en la via publica. El reporte medico indica que la victima recibio una unica herida por arma blanca en la región del hipocondrio derecho. El paciente ingresó inconsciente, con hipotensión severa y shoch hipovolémico refractario. Fallecio a los 45 minutos de su ingreso a pesar de las intervenciones.</t>
+  </si>
+  <si>
+    <t>Ausente</t>
+  </si>
+  <si>
+    <t>Primeras 12 horas el cuerpo pierde 1°C cada hora</t>
+  </si>
+  <si>
+    <t>La temperatura nunca bajará más allá de la temperatura del lugar donde se encuentra</t>
+  </si>
+  <si>
+    <t>Muerte por traumatismo creaneoencefálico</t>
+  </si>
+  <si>
+    <t>Muerte por paro cardiaco a las 4:00 hrs</t>
+  </si>
+  <si>
+    <t>Muerte por choque hipovolémico</t>
+  </si>
+  <si>
+    <t>Caso #03</t>
+  </si>
+  <si>
+    <t>En el alféizar de una ventana del sexto piso, una mujer salta. Sin embargo, no se mata ni sufre ningun tipo de secuelas</t>
+  </si>
+  <si>
+    <t>----</t>
+  </si>
+  <si>
+    <t>-----</t>
+  </si>
+  <si>
+    <t>Salto dentro del apartamento</t>
+  </si>
+  <si>
+    <t>La mujer murio por otra causa</t>
+  </si>
+  <si>
+    <t>Salto dentro del departamento</t>
+  </si>
+  <si>
+    <t>Tomo un veneno</t>
   </si>
 </sst>
 </file>
@@ -465,7 +513,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -502,6 +550,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -933,8 +984,8 @@
       <c r="B3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>29</v>
+      <c r="C3" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>30</v>
@@ -979,77 +1030,77 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>29</v>
+      <c r="B4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4">
-        <v>28</v>
-      </c>
-      <c r="F4">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4">
-        <v>70</v>
-      </c>
-      <c r="J4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4" t="s">
-        <v>66</v>
-      </c>
-      <c r="M4" t="s">
-        <v>67</v>
-      </c>
-      <c r="N4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O4" t="s">
-        <v>68</v>
+        <v>107</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="N4" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="O4" s="18" t="s">
+        <v>112</v>
       </c>
       <c r="P4" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="Q4" s="18" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>70</v>
+      <c r="B5" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
         <v>20</v>
@@ -1058,7 +1109,7 @@
         <v>21</v>
       </c>
       <c r="I5">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J5" t="s">
         <v>22</v>
@@ -1085,110 +1136,110 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="I6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J6" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L6" t="s">
         <v>66</v>
       </c>
       <c r="M6" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="N6" t="s">
         <v>25</v>
       </c>
       <c r="O6" t="s">
+        <v>68</v>
+      </c>
+      <c r="P6" t="s">
         <v>69</v>
       </c>
-      <c r="P6" t="s">
-        <v>76</v>
-      </c>
       <c r="Q6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7">
+        <v>27</v>
+      </c>
+      <c r="F7">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7">
         <v>80</v>
       </c>
-      <c r="G7" t="s">
-        <v>82</v>
-      </c>
-      <c r="H7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I7" t="s">
-        <v>81</v>
-      </c>
       <c r="J7" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L7" t="s">
         <v>66</v>
       </c>
       <c r="M7" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="N7" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="O7" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P7" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="Q7" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
@@ -1196,104 +1247,201 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" t="s">
-        <v>87</v>
+      <c r="D8" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>79</v>
       </c>
       <c r="F8" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="I8" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J8" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="K8">
-        <v>25</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>94</v>
+        <v>3</v>
+      </c>
+      <c r="L8" t="s">
+        <v>66</v>
       </c>
       <c r="M8" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="N8" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="O8" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="Q8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9">
+        <v>25</v>
+      </c>
+      <c r="F9">
+        <v>22</v>
+      </c>
+      <c r="G9" t="s">
+        <v>100</v>
+      </c>
+      <c r="H9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9">
+        <v>70</v>
+      </c>
+      <c r="J9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9">
+        <v>0.5</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="P9" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q9" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>89</v>
+      </c>
+      <c r="J10" t="s">
+        <v>90</v>
+      </c>
+      <c r="K10">
+        <v>25</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M10" t="s">
+        <v>97</v>
+      </c>
+      <c r="N10" t="s">
+        <v>91</v>
+      </c>
+      <c r="O10" t="s">
+        <v>92</v>
+      </c>
+      <c r="P10" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E11" s="2">
         <v>25</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F11" s="2">
         <v>18</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I11" s="2">
         <v>90</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K11" s="2">
         <v>28</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="L11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="M11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="2"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="2"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
